--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/classifier_prediction/tables/prediction_probabilities.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/classifier_prediction/tables/prediction_probabilities.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,13 +465,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7457462003331216</v>
+        <v>0.8948956100897444</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2542529317701611</v>
+        <v>0.1051043556465499</v>
       </c>
       <c r="E2" t="n">
-        <v>8.678967173354972e-07</v>
+        <v>3.426370573382467e-08</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001915218141296037</v>
+        <v>0.002422486260009598</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9979955318286146</v>
+        <v>0.9975774455467934</v>
       </c>
       <c r="E3" t="n">
-        <v>8.925003008935828e-05</v>
+        <v>6.819319713866487e-08</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02366238445795562</v>
+        <v>0.0153068005903759</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8811748184556556</v>
+        <v>0.09621009329512319</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09516279708638868</v>
+        <v>0.8884831061145009</v>
       </c>
     </row>
     <row r="5">
@@ -522,13 +522,13 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1712730179314094</v>
+        <v>0.3698331709243715</v>
       </c>
       <c r="D5" t="n">
-        <v>0.828335766035344</v>
+        <v>0.6301475282930732</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003912160332466167</v>
+        <v>1.930078255537561e-05</v>
       </c>
     </row>
     <row r="6">
@@ -541,13 +541,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06044328846714848</v>
+        <v>0.1412407825784759</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9395117192312761</v>
+        <v>0.8587581892764435</v>
       </c>
       <c r="E6" t="n">
-        <v>4.499230157548964e-05</v>
+        <v>1.028145080691311e-06</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01203804606666485</v>
+        <v>0.01928114299379395</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9876090793100969</v>
+        <v>0.9807144793754192</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003528746232380909</v>
+        <v>4.377630786828878e-06</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005271416229946495</v>
+        <v>0.01604131378531548</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9931134537610056</v>
+        <v>0.9836427477429608</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001615130009047871</v>
+        <v>0.00031593847172391</v>
       </c>
     </row>
     <row r="9">
@@ -598,13 +598,13 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4073116215064904</v>
+        <v>0.2816555837151625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.592681351151386</v>
+        <v>0.718344384918251</v>
       </c>
       <c r="E9" t="n">
-        <v>7.027342123636675e-06</v>
+        <v>3.136658645574766e-08</v>
       </c>
     </row>
     <row r="10">
@@ -617,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1722821345745588</v>
+        <v>0.0978826581358446</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8277076392548177</v>
+        <v>0.9021173272203842</v>
       </c>
       <c r="E10" t="n">
-        <v>1.022617062342068e-05</v>
+        <v>1.464377118464043e-08</v>
       </c>
     </row>
     <row r="11">
@@ -636,13 +636,13 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0004778521308079619</v>
+        <v>0.000401717573461519</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9994145655199304</v>
+        <v>0.9995982470060009</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001075823492616769</v>
+        <v>3.542053766860478e-08</v>
       </c>
     </row>
     <row r="12">
@@ -655,13 +655,13 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02185464548617507</v>
+        <v>0.04044412587601381</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9779972122614919</v>
+        <v>0.9595498708778082</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0001481422523330115</v>
+        <v>6.003246178046146e-06</v>
       </c>
     </row>
     <row r="13">
@@ -674,1856 +674,1932 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9821576170788042</v>
+        <v>0.9839143857127429</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01784236956776372</v>
+        <v>0.01608561183873494</v>
       </c>
       <c r="E13" t="n">
-        <v>1.335343204350509e-08</v>
+        <v>2.448522080600426e-09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>019B</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9859349115910648</v>
+        <v>0.02885035691261621</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01406508797779889</v>
+        <v>0.9710921664375616</v>
       </c>
       <c r="E14" t="n">
-        <v>4.311361282530446e-10</v>
+        <v>5.747664982210498e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>021B</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9541449161725549</v>
+        <v>0.9425336749007794</v>
       </c>
       <c r="D15" t="n">
-        <v>0.04585507890102733</v>
+        <v>0.05746632509876617</v>
       </c>
       <c r="E15" t="n">
-        <v>4.926417765158036e-09</v>
+        <v>4.543346638367357e-13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>022B</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001077905636946715</v>
+        <v>0.9520218418183762</v>
       </c>
       <c r="D16" t="n">
-        <v>0.999688768145534</v>
+        <v>0.04797815807734225</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0002034412907713158</v>
+        <v>1.042815822692991e-10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>023C</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2923195292126455</v>
+        <v>9.253655349365204e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6802830338033997</v>
+        <v>0.9999074066454086</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02739743698395486</v>
+        <v>5.680109782248075e-08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>024C</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>3.639406356581355e-05</v>
+        <v>0.06250229410717008</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9903165426494904</v>
+        <v>0.01897375460620483</v>
       </c>
       <c r="E18" t="n">
-        <v>0.009647063286943631</v>
+        <v>0.9185239512866251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>025B</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9707136081908728</v>
+        <v>0.0001410084515367426</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02928638110123135</v>
+        <v>0.9976333723359672</v>
       </c>
       <c r="E19" t="n">
-        <v>1.070789571894356e-08</v>
+        <v>0.002225619212496051</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>027B</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.983087632465937</v>
+        <v>0.9940718647240342</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01691234456248237</v>
+        <v>0.005928132018482424</v>
       </c>
       <c r="E20" t="n">
-        <v>2.297158059828812e-08</v>
+        <v>3.257483427462233e-09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>029C</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9914519201668958</v>
+        <v>0.9948698767804107</v>
       </c>
       <c r="D21" t="n">
-        <v>0.007326238714431422</v>
+        <v>0.00513011953324073</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001221841118672778</v>
+        <v>3.686348607444947e-09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>031A</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1.247789926320954e-15</v>
+        <v>0.01028519671245398</v>
       </c>
       <c r="D22" t="n">
-        <v>1.052288646156173e-14</v>
+        <v>2.486667987061417e-06</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999999999999882</v>
+        <v>0.9897123166195589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>034C</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.522998760667327e-33</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.912101660145437e-36</v>
+      </c>
+      <c r="E23" t="n">
         <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.9932794081517633</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.006720257359627967</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3.344886087678755e-07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>037B</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>5.025233145416106e-21</v>
+        <v>0.9975165409140543</v>
       </c>
       <c r="D24" t="n">
-        <v>4.616963984661644e-15</v>
+        <v>0.002477277729152843</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999999999999953</v>
+        <v>6.181356792847691e-06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>042C</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003374583937810805</v>
+        <v>6.002965712435143e-35</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9961277857682186</v>
+        <v>2.249266952936631e-32</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0004976302939705605</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>043ABC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>8.995042783052085e-07</v>
+        <v>0.991941821652783</v>
       </c>
       <c r="D26" t="n">
-        <v>0.006812517217058839</v>
+        <v>0.002917150318917976</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9931865832786629</v>
+        <v>0.005141028028298978</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>044A</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9643099392737824</v>
+        <v>0.01877065754832115</v>
       </c>
       <c r="D27" t="n">
-        <v>0.03569005980235865</v>
+        <v>0.981097360229234</v>
       </c>
       <c r="E27" t="n">
-        <v>9.238588286585103e-10</v>
+        <v>0.0001319822224447388</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>045B</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9769044142474294</v>
+        <v>6.522587753614706e-10</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02309558242288531</v>
+        <v>1.042067874334171e-07</v>
       </c>
       <c r="E28" t="n">
-        <v>3.329685349686473e-09</v>
+        <v>0.9999998951409538</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>047ABC</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9613183610834731</v>
+        <v>0.9673017762529874</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03603916725326028</v>
+        <v>0.03269822373953205</v>
       </c>
       <c r="E29" t="n">
-        <v>0.002642471663266494</v>
+        <v>7.480608589435301e-12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>048C</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1.002901302972158e-08</v>
+        <v>0.9731147781396069</v>
       </c>
       <c r="D30" t="n">
-        <v>8.971269252554683e-07</v>
+        <v>0.02688522184336298</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9999990928440616</v>
+        <v>1.703006584113407e-11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>049A</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006150099995419453</v>
+        <v>0.04604662687102348</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9938204735811128</v>
+        <v>0.0001032309456904728</v>
       </c>
       <c r="E31" t="n">
-        <v>2.942642346774442e-05</v>
+        <v>0.953850142183286</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>052B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9955187165976491</v>
+        <v>9.973993991305056e-17</v>
       </c>
       <c r="D32" t="n">
-        <v>0.004481282713120181</v>
+        <v>5.944465165662295e-17</v>
       </c>
       <c r="E32" t="n">
-        <v>6.892307280589571e-10</v>
+        <v>0.9999999999999998</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>054B</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9851174408907117</v>
+        <v>0.00761231277860092</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01488255345612994</v>
+        <v>0.9923874377498585</v>
       </c>
       <c r="E33" t="n">
-        <v>5.653158247228698e-09</v>
+        <v>2.494715405870236e-07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>055C</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0006252035925213772</v>
+        <v>0.9951333987948512</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9775150149353299</v>
+        <v>0.004866601196948856</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02185978147214861</v>
+        <v>8.200081797523415e-12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>057C</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001152601294732717</v>
+        <v>0.9919324381849295</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9663214243246461</v>
+        <v>0.008067561225917449</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03252597438062119</v>
+        <v>5.891528887700969e-10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>059ABC</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>7.848701713305491e-07</v>
+        <v>0.005490669103680335</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01310842202444349</v>
+        <v>0.4287835543589695</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9868907931053853</v>
+        <v>0.5657257765373501</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>065C</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>1.186158181127661e-07</v>
+        <v>0.002180001600860237</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0004452394072477675</v>
+        <v>0.9954142738339254</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9995546419769341</v>
+        <v>0.002405724565214499</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>067B</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>2.680702806612246e-07</v>
+        <v>4.204952528400571e-09</v>
       </c>
       <c r="D38" t="n">
-        <v>0.006011589438636543</v>
+        <v>4.317724466346541e-06</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9939881424910828</v>
+        <v>0.9999956780705811</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>069A</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9867271651627439</v>
+        <v>2.1685127328338e-11</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01327280867955415</v>
+        <v>2.434313370789399e-09</v>
       </c>
       <c r="E39" t="n">
-        <v>2.615770192263604e-08</v>
+        <v>0.9999999975440015</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>070B</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>0.003291597180970926</v>
+        <v>9.154243581466099e-10</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9260667223462554</v>
+        <v>1.084881680497933e-06</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07064168047277364</v>
+        <v>0.9999989142028952</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.09995204567998946</v>
+        <v>0.958444455255194</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8984173574469237</v>
+        <v>0.04155554459224257</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001630596873086703</v>
+        <v>1.525635813340881e-10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>072A</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01090274452830954</v>
+        <v>0.009701487539789399</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8619542785015277</v>
+        <v>0.9461236636307325</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1271429769701627</v>
+        <v>0.04417484882947819</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>075A</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003117720465383194</v>
+        <v>0.1694163960468578</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9533678979808472</v>
+        <v>0.8297450540044925</v>
       </c>
       <c r="E43" t="n">
-        <v>0.04351438155376962</v>
+        <v>0.0008385499486495212</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>077B</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>3.288710820241146e-09</v>
+        <v>0.01141733889415306</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0003409885165023372</v>
+        <v>0.4768670186014961</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9996590081947868</v>
+        <v>0.5117156425043509</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>078B</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0002074257328969218</v>
+        <v>0.009173168291330658</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9996355811993906</v>
+        <v>0.9698589467926643</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0001569930677127384</v>
+        <v>0.02096788491600515</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>079C</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>3.759378098470867e-07</v>
+        <v>2.61527096394265e-13</v>
       </c>
       <c r="D46" t="n">
-        <v>5.836409416448711e-05</v>
+        <v>6.088127888233933e-10</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9999412599680257</v>
+        <v>0.9999999993909257</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>080C</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>1.037147472944795e-06</v>
+        <v>0.0008885214488218916</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01082431594821052</v>
+        <v>0.9990903740563223</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9891746469043166</v>
+        <v>2.110449485585005e-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>081B</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>0.8102368023694909</v>
+        <v>2.235373004161569e-12</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1897606300423983</v>
+        <v>2.611066768382007e-12</v>
       </c>
       <c r="E48" t="n">
-        <v>2.567588110653573e-06</v>
+        <v>0.9999999999951537</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>082A</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>9.689776414821807e-05</v>
+        <v>4.448354411730903e-10</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5524366625463918</v>
+        <v>6.987038202028194e-08</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4474664396894599</v>
+        <v>0.9999999296847827</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>083B</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.002724147374622483</v>
+        <v>0.8468347959529979</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9912578493418893</v>
+        <v>0.1531650571099945</v>
       </c>
       <c r="E50" t="n">
-        <v>0.006018003283488294</v>
+        <v>1.469370075669814e-07</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>084A</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
-        <v>0.003680550867752619</v>
+        <v>2.011769838717975e-05</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9909982186584997</v>
+        <v>0.006862068376481733</v>
       </c>
       <c r="E51" t="n">
-        <v>0.005321230473747674</v>
+        <v>0.9931178139251311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>085C</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>0.01252282083923095</v>
+        <v>0.02912038922589897</v>
       </c>
       <c r="D52" t="n">
-        <v>0.001656975270410859</v>
+        <v>0.9115990352723656</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9858202038903582</v>
+        <v>0.05928057550173534</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>086A</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>1.09766531372415e-07</v>
+        <v>0.04029835687552639</v>
       </c>
       <c r="D53" t="n">
-        <v>0.002113685248150198</v>
+        <v>0.8993645404749004</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9978862049853185</v>
+        <v>0.06033710264957327</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>088C</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9966033664890627</v>
+        <v>2.712313758368679e-08</v>
       </c>
       <c r="D54" t="n">
-        <v>0.003394320846254701</v>
+        <v>8.220502392684967e-11</v>
       </c>
       <c r="E54" t="n">
-        <v>2.312664682611946e-06</v>
+        <v>0.9999999727946575</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>089A</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>1.763135679484149e-11</v>
+        <v>4.2698565910024e-11</v>
       </c>
       <c r="D55" t="n">
-        <v>1.584733983770414e-07</v>
+        <v>1.409763857117298e-08</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9999998415089701</v>
+        <v>0.9999999858596629</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>090B</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00206621740754718</v>
+        <v>0.9982226435717527</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9913673335210836</v>
+        <v>0.001774182229037621</v>
       </c>
       <c r="E56" t="n">
-        <v>0.006566449071369188</v>
+        <v>3.174199209657549e-06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>091C</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1929890624969074</v>
+        <v>7.697835955453813e-19</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4614007346579121</v>
+        <v>2.368789336298774e-17</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3456102028451805</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>092ABC</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8738850105294788</v>
+        <v>0.01528835662846951</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1258835814077598</v>
+        <v>0.9645358681877145</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0002314080627614116</v>
+        <v>0.02017577518381612</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>093C</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0002964443316068236</v>
+        <v>0.03312894052462026</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9989619008341921</v>
+        <v>0.01238903022207947</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0007416548342011419</v>
+        <v>0.9544820292533004</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0009459103665520167</v>
+        <v>0.9588197061682049</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9486259913318826</v>
+        <v>0.04108450115405415</v>
       </c>
       <c r="E60" t="n">
-        <v>0.05042809830156536</v>
+        <v>9.57926777410476e-05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>095A</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>1.027050255494879e-07</v>
+        <v>0.0006240081965043898</v>
       </c>
       <c r="D61" t="n">
-        <v>2.222447176302265e-05</v>
+        <v>0.9993720224921478</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9999776728232114</v>
+        <v>3.969311347675686e-06</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>096A</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>8.58969049093354e-06</v>
+        <v>0.002203830565309257</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0179775453069718</v>
+        <v>0.1096985662532899</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9820138650025373</v>
+        <v>0.8880976031814007</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>097ABC</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>0.004598383947548387</v>
+        <v>2.966189269868403e-13</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9941133600635335</v>
+        <v>4.097478392763623e-13</v>
       </c>
       <c r="E63" t="n">
-        <v>0.001288255988918074</v>
+        <v>0.9999999999992937</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>098C</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>5.990362035602365e-08</v>
+        <v>0.9275527239272232</v>
       </c>
       <c r="D64" t="n">
-        <v>5.470395660189165e-05</v>
+        <v>0.07086433197602376</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9999452361397778</v>
+        <v>0.001582944096753102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>099C</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003599637081997609</v>
+        <v>9.55118201736317e-09</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9947526653208565</v>
+        <v>4.819011045068009e-07</v>
       </c>
       <c r="E65" t="n">
-        <v>0.001647697597145814</v>
+        <v>0.9999995085477135</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>0.01610633149160522</v>
+        <v>0.0443275538535555</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9838329988062572</v>
+        <v>0.9501691730622553</v>
       </c>
       <c r="E66" t="n">
-        <v>6.066970213752808e-05</v>
+        <v>0.005503273084189303</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>101C</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2311144509150123</v>
+        <v>1.128539050337517e-14</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7688633577361099</v>
+        <v>2.334001390300746e-14</v>
       </c>
       <c r="E67" t="n">
-        <v>2.219134887763648e-05</v>
+        <v>0.9999999999999654</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>102B</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0008204210506207763</v>
+        <v>0.00600696375789095</v>
       </c>
       <c r="D68" t="n">
-        <v>0.7725329007540309</v>
+        <v>0.9939782206503335</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2266466781953483</v>
+        <v>1.481559177555904e-05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>103A</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>0.03495454211052646</v>
+        <v>0.1207092751854553</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9647842405211456</v>
+        <v>0.8792599111483203</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0002612173683278885</v>
+        <v>3.081366622453907e-05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>104C</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>1.894734625157941e-05</v>
+        <v>0.3601799227375047</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1168906979830035</v>
+        <v>0.6398182553996354</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8830903546707449</v>
+        <v>1.821862859989713e-06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>105C</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>1.055894892839887e-09</v>
+        <v>2.666998835734228e-05</v>
       </c>
       <c r="D71" t="n">
-        <v>6.245931105153778e-05</v>
+        <v>0.000885163799406944</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9999375396330534</v>
+        <v>0.9990881662122357</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>106B</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0009780700845448524</v>
+        <v>0.2517836253851793</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9988233710093632</v>
+        <v>0.7465323079866737</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0001985589060919067</v>
+        <v>0.001684066628147007</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>107C</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05003322832442185</v>
+        <v>1.764285768416355e-07</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9499638554585123</v>
+        <v>5.720084598678272e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>2.91621706581713e-06</v>
+        <v>0.9999426227254363</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>108B</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>0.07578359743529905</v>
+        <v>2.828967722910196e-13</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9241972039656182</v>
+        <v>7.960669161207361e-10</v>
       </c>
       <c r="E74" t="n">
-        <v>1.919859908277402e-05</v>
+        <v>0.9999999992036501</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t xml:space="preserve">111C </t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0005457902736346283</v>
+        <v>0.00369751172487123</v>
       </c>
       <c r="D75" t="n">
-        <v>0.7867013590455515</v>
+        <v>0.9962848021531213</v>
       </c>
       <c r="E75" t="n">
-        <v>0.212752850680814</v>
+        <v>1.76861220075992e-05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>113B</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>0.01847471802765377</v>
+        <v>0.05185905016840257</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9815137697552697</v>
+        <v>0.9481409419197917</v>
       </c>
       <c r="E76" t="n">
-        <v>1.151221707643813e-05</v>
+        <v>7.911805689624577e-09</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>114B</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1158404426520684</v>
+        <v>0.1653380398237763</v>
       </c>
       <c r="D77" t="n">
-        <v>0.8841222288612828</v>
+        <v>0.834659370318108</v>
       </c>
       <c r="E77" t="n">
-        <v>3.732848664892918e-05</v>
+        <v>2.589858115623093e-06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>115ABC</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1772075113016671</v>
+        <v>0.001396848014886719</v>
       </c>
       <c r="D78" t="n">
-        <v>0.82172653396486</v>
+        <v>0.3242778629290512</v>
       </c>
       <c r="E78" t="n">
-        <v>0.001065954733472803</v>
+        <v>0.674325289056062</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>116B</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>0.00134825874232066</v>
+        <v>0.02247598965561435</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9980694587093693</v>
+        <v>0.9775239793857124</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0005822825483100665</v>
+        <v>3.095867327687391e-08</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>117ABC</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>4.56461436458846e-06</v>
+        <v>0.2085776169861762</v>
       </c>
       <c r="D80" t="n">
-        <v>0.002910304862918604</v>
+        <v>0.7914190092324933</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9970851305227167</v>
+        <v>3.373781330617739e-06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>118A</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>1.986340921160007e-05</v>
+        <v>0.5176665446867121</v>
       </c>
       <c r="D81" t="n">
-        <v>0.008429118761640614</v>
+        <v>0.4677199729887503</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9915510178291478</v>
+        <v>0.01461348232453755</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>119B</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0008966012207559936</v>
+        <v>0.005690943312225287</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7616054361013502</v>
+        <v>0.9941323569662485</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2374979626778938</v>
+        <v>0.0001766997215263305</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>123A</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0007989992862783995</v>
+        <v>1.25869697666771e-10</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9809844222488888</v>
+        <v>1.57082769506431e-09</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01821657846483273</v>
+        <v>0.9999999983033026</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>124A</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>0.003511114928048627</v>
+        <v>2.808509735836e-09</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9955308431886789</v>
+        <v>3.057624172436286e-08</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0009580418832724634</v>
+        <v>0.9999999666152486</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>126A</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
-        <v>0.01130055480608526</v>
+        <v>0.001353530927670325</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9881675937284964</v>
+        <v>0.1360647689780893</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0005318514654185866</v>
+        <v>0.8625817000942404</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>127B</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>6.014110215921029e-06</v>
+        <v>0.002925230449630465</v>
       </c>
       <c r="D86" t="n">
-        <v>0.01180878710339056</v>
+        <v>0.9800022635289887</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9881851987863935</v>
+        <v>0.01707250602138093</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>128B</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>1.084344467483526e-06</v>
+        <v>0.0130877800065342</v>
       </c>
       <c r="D87" t="n">
-        <v>0.001715836459954403</v>
+        <v>0.986755992937425</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9982830791955781</v>
+        <v>0.0001562270560407667</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>129A</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>0.003420966093329896</v>
+        <v>0.01020507762630424</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9965061041729348</v>
+        <v>0.9897937231981828</v>
       </c>
       <c r="E88" t="n">
-        <v>7.292973373514455e-05</v>
+        <v>1.199175512976829e-06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>130A</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0007170207529356537</v>
+        <v>3.558055803348407e-08</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4249915642918178</v>
+        <v>4.581150629983785e-06</v>
       </c>
       <c r="E89" t="n">
-        <v>0.5742914149552465</v>
+        <v>0.999995383268812</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>131B</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0007758849948021375</v>
+        <v>1.001074007980258e-09</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4107579313853086</v>
+        <v>8.796488710167411e-08</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5884661836198893</v>
+        <v>0.9999999110340388</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>134C</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>0.002783139988015057</v>
+        <v>0.002713299534228281</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9902429272500891</v>
+        <v>0.9972866744899823</v>
       </c>
       <c r="E91" t="n">
-        <v>0.006973932761895714</v>
+        <v>2.597578929926177e-08</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>135A</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0007142796087370008</v>
+        <v>6.84784287184799e-05</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9724337184461338</v>
+        <v>0.002953352788805578</v>
       </c>
       <c r="E92" t="n">
-        <v>0.02685200194512918</v>
+        <v>0.9969781687824759</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>136B</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
-        <v>0.002506992912646703</v>
+        <v>0.001976188136306995</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9967437380522778</v>
+        <v>0.4964429356447714</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0007492690350756277</v>
+        <v>0.5015808762189217</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>137A</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>0.000587876598460031</v>
+        <v>0.001112177860219219</v>
       </c>
       <c r="D94" t="n">
-        <v>0.5383662737502659</v>
+        <v>0.9988861860087407</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4610458496512741</v>
+        <v>1.636131040120548e-06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>138B</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0008364731640923293</v>
+        <v>0.001285613593171523</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8277080294624134</v>
+        <v>0.9963922009705083</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1714554973734944</v>
+        <v>0.002322185436320321</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>140C</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>0.008853769916192895</v>
+        <v>0.002935267781595265</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9904064717476452</v>
+        <v>0.9970615389506862</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0007397583361617774</v>
+        <v>3.193267718542513e-06</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>141B</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01019194852711297</v>
+        <v>0.0002178890886699197</v>
       </c>
       <c r="D97" t="n">
-        <v>0.8980614577798314</v>
+        <v>0.0377556185604843</v>
       </c>
       <c r="E97" t="n">
-        <v>0.09174659369305563</v>
+        <v>0.9620264923508458</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>142C</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C98" t="n">
-        <v>0.008028525783279467</v>
+        <v>0.002435486723097899</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9736719342655896</v>
+        <v>0.3808188374601186</v>
       </c>
       <c r="E98" t="n">
-        <v>0.01829953995113091</v>
+        <v>0.6167456758167836</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>143B</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>3.744356031018922e-07</v>
+        <v>0.02129611635750965</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0008591355258217299</v>
+        <v>0.9786557276137768</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9991404900385752</v>
+        <v>4.815602871361348e-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>144B</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03810042317536025</v>
+        <v>0.01976958764318053</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9615244624193111</v>
+        <v>0.3519668184971125</v>
       </c>
       <c r="E100" t="n">
-        <v>0.000375114405328729</v>
+        <v>0.6282635938597069</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>145B</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0004190457264656885</v>
+        <v>0.02178813337555921</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9560505103430532</v>
+        <v>0.9673853290976119</v>
       </c>
       <c r="E101" t="n">
-        <v>0.04353044393048106</v>
+        <v>0.01082653752682882</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>146B</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102" t="n">
-        <v>0.9957666760282288</v>
+        <v>1.26575468563355e-10</v>
       </c>
       <c r="D102" t="n">
-        <v>0.004233286086501349</v>
+        <v>1.304257134834095e-08</v>
       </c>
       <c r="E102" t="n">
-        <v>3.788526991913655e-08</v>
+        <v>0.9999999868308533</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>148B</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>0.002045871657927936</v>
+        <v>0.05013566174397865</v>
       </c>
       <c r="D103" t="n">
-        <v>0.04636405330239766</v>
+        <v>0.9498553783831524</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9515900750396744</v>
+        <v>8.959872868830939e-06</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>149C</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>2</v>
       </c>
       <c r="C104" t="n">
-        <v>0.06911668590532753</v>
+        <v>0.00167919124194334</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9072286349182266</v>
+        <v>0.968265732683898</v>
       </c>
       <c r="E104" t="n">
-        <v>0.02365467917644594</v>
+        <v>0.03005507607415864</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>150B</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105" t="n">
-        <v>0.9937519011497439</v>
+        <v>9.716423772778057e-07</v>
       </c>
       <c r="D105" t="n">
-        <v>0.006247571247406364</v>
+        <v>3.663744554619978e-06</v>
       </c>
       <c r="E105" t="n">
-        <v>5.276028498524247e-07</v>
+        <v>0.999995364613068</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>S83</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>0.04424782602085297</v>
+        <v>0.9878241090143082</v>
       </c>
       <c r="D106" t="n">
-        <v>0.8650985980818392</v>
+        <v>0.01217588986293535</v>
       </c>
       <c r="E106" t="n">
-        <v>0.09065357589730795</v>
+        <v>1.122756410337171e-09</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>S84</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107" t="n">
-        <v>0.9905950406298789</v>
+        <v>7.920305408165864e-08</v>
       </c>
       <c r="D107" t="n">
-        <v>0.009404917089931693</v>
+        <v>2.43563775542589e-08</v>
       </c>
       <c r="E107" t="n">
-        <v>4.228018951567813e-08</v>
+        <v>0.9999998964405684</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>S85</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>3</v>
       </c>
       <c r="C108" t="n">
-        <v>8.458601851550704e-06</v>
+        <v>0.153919045682663</v>
       </c>
       <c r="D108" t="n">
-        <v>0.01968436193292363</v>
+        <v>0.2862241853837416</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9803071794652248</v>
+        <v>0.5598567689335954</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>S87</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2055850067964611</v>
+        <v>0.9943055810494487</v>
       </c>
       <c r="D109" t="n">
-        <v>0.7944141230622529</v>
+        <v>0.005693885014425199</v>
       </c>
       <c r="E109" t="n">
-        <v>8.701412859097939e-07</v>
+        <v>5.339361260695693e-07</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
+          <t>S89</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.05350519161334428</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.3944146587671373</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.5520801496195183</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.9896078351380111</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.01039216194533906</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2.916649821854294e-09</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>S94</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1.039106516357234e-07</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2.242472545445629e-05</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9999774713638938</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>S95</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.0417071808316864</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.9582928190812393</v>
+      </c>
+      <c r="E113" t="n">
+        <v>8.707430226777605e-11</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
           <t>S98</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>3</v>
-      </c>
-      <c r="C110" t="n">
-        <v>1.020774629836657e-07</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0.0002217314717728642</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0.9997781664507642</v>
+      <c r="B114" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" t="n">
+        <v>8.301479752570582e-13</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1.702809708029078e-11</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9999999999821418</v>
       </c>
     </row>
   </sheetData>
